--- a/import-template/cau_hinh_template.xlsx
+++ b/import-template/cau_hinh_template.xlsx
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Import bằng lệnh: python tools/import_config.py &lt;đường-dẫn-file&gt;.xlsx</t>
+          <t>Import: trang Admin → tab Import, hoặc lệnh python tools/import_config.py &lt;file&gt;.xlsx</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
